--- a/data/nzd0155/nzd0155.xlsx
+++ b/data/nzd0155/nzd0155.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K666"/>
+  <dimension ref="A1:K671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26404,6 +26404,201 @@
         <v>330.16</v>
       </c>
       <c r="K666" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>335</v>
+      </c>
+      <c r="C667" t="n">
+        <v>331.03</v>
+      </c>
+      <c r="D667" t="n">
+        <v>337.09</v>
+      </c>
+      <c r="E667" t="n">
+        <v>351.88</v>
+      </c>
+      <c r="F667" t="n">
+        <v>350.31</v>
+      </c>
+      <c r="G667" t="n">
+        <v>344.94</v>
+      </c>
+      <c r="H667" t="n">
+        <v>345.94</v>
+      </c>
+      <c r="I667" t="n">
+        <v>338.23</v>
+      </c>
+      <c r="J667" t="n">
+        <v>329.21</v>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>334.85</v>
+      </c>
+      <c r="C668" t="n">
+        <v>331.13</v>
+      </c>
+      <c r="D668" t="n">
+        <v>337.16</v>
+      </c>
+      <c r="E668" t="n">
+        <v>351.77</v>
+      </c>
+      <c r="F668" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="G668" t="n">
+        <v>344.37</v>
+      </c>
+      <c r="H668" t="n">
+        <v>345.43</v>
+      </c>
+      <c r="I668" t="n">
+        <v>336.4</v>
+      </c>
+      <c r="J668" t="n">
+        <v>328.59</v>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>334.92</v>
+      </c>
+      <c r="C669" t="n">
+        <v>331.38</v>
+      </c>
+      <c r="D669" t="n">
+        <v>337.75</v>
+      </c>
+      <c r="E669" t="n">
+        <v>352.2</v>
+      </c>
+      <c r="F669" t="n">
+        <v>350.69</v>
+      </c>
+      <c r="G669" t="n">
+        <v>345.29</v>
+      </c>
+      <c r="H669" t="n">
+        <v>346.31</v>
+      </c>
+      <c r="I669" t="n">
+        <v>337.93</v>
+      </c>
+      <c r="J669" t="n">
+        <v>328.75</v>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="n">
+        <v>334.62</v>
+      </c>
+      <c r="C670" t="n">
+        <v>331.3</v>
+      </c>
+      <c r="D670" t="n">
+        <v>337.79</v>
+      </c>
+      <c r="E670" t="n">
+        <v>352.23</v>
+      </c>
+      <c r="F670" t="n">
+        <v>350.84</v>
+      </c>
+      <c r="G670" t="n">
+        <v>345.59</v>
+      </c>
+      <c r="H670" t="n">
+        <v>346.95</v>
+      </c>
+      <c r="I670" t="n">
+        <v>338.95</v>
+      </c>
+      <c r="J670" t="n">
+        <v>329.02</v>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>334.45</v>
+      </c>
+      <c r="C671" t="n">
+        <v>331.48</v>
+      </c>
+      <c r="D671" t="n">
+        <v>338.38</v>
+      </c>
+      <c r="E671" t="n">
+        <v>352.81</v>
+      </c>
+      <c r="F671" t="n">
+        <v>351.01</v>
+      </c>
+      <c r="G671" t="n">
+        <v>346.21</v>
+      </c>
+      <c r="H671" t="n">
+        <v>347.33</v>
+      </c>
+      <c r="I671" t="n">
+        <v>339.67</v>
+      </c>
+      <c r="J671" t="n">
+        <v>330.43</v>
+      </c>
+      <c r="K671" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26420,7 +26615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B682"/>
+  <dimension ref="A1:B687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33243,6 +33438,56 @@
       </c>
       <c r="B682" t="n">
         <v>-0.89</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>-1.23</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>-0.3</v>
       </c>
     </row>
   </sheetData>
@@ -33411,28 +33656,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3975898399720261</v>
+        <v>-0.4069803215152752</v>
       </c>
       <c r="J2" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="K2" t="n">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="L2" t="n">
-        <v>0.363795150154974</v>
+        <v>0.3739758763894523</v>
       </c>
       <c r="M2" t="n">
-        <v>3.062325872899401</v>
+        <v>3.084875679646953</v>
       </c>
       <c r="N2" t="n">
-        <v>15.92275880460476</v>
+        <v>16.11322506933115</v>
       </c>
       <c r="O2" t="n">
-        <v>3.990333169624406</v>
+        <v>4.014128182972132</v>
       </c>
       <c r="P2" t="n">
-        <v>352.0080539950454</v>
+        <v>352.1074574003287</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33489,28 +33734,28 @@
         <v>0.0409</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4408765016921832</v>
+        <v>-0.4509613708819295</v>
       </c>
       <c r="J3" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="K3" t="n">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4143696023700434</v>
+        <v>0.4239127384283863</v>
       </c>
       <c r="M3" t="n">
-        <v>3.054093970292964</v>
+        <v>3.08703410616915</v>
       </c>
       <c r="N3" t="n">
-        <v>15.82258060298597</v>
+        <v>16.06122481329985</v>
       </c>
       <c r="O3" t="n">
-        <v>3.977760752356276</v>
+        <v>4.007645794390998</v>
       </c>
       <c r="P3" t="n">
-        <v>350.1512095068269</v>
+        <v>350.2579578889014</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33567,28 +33812,28 @@
         <v>0.0409</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4965323685598126</v>
+        <v>-0.5033136640904552</v>
       </c>
       <c r="J4" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="K4" t="n">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4099353401103886</v>
+        <v>0.4185639345566653</v>
       </c>
       <c r="M4" t="n">
-        <v>3.626564818021865</v>
+        <v>3.641299127636487</v>
       </c>
       <c r="N4" t="n">
-        <v>20.44029056800439</v>
+        <v>20.45058688497634</v>
       </c>
       <c r="O4" t="n">
-        <v>4.521093956998061</v>
+        <v>4.522232511158215</v>
       </c>
       <c r="P4" t="n">
-        <v>355.7342244008591</v>
+        <v>355.805998495508</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33645,28 +33890,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2472368974645181</v>
+        <v>-0.2478547211844259</v>
       </c>
       <c r="J5" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="K5" t="n">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2115495741263568</v>
+        <v>0.2151151701846582</v>
       </c>
       <c r="M5" t="n">
-        <v>2.748764626523615</v>
+        <v>2.732309819719831</v>
       </c>
       <c r="N5" t="n">
-        <v>13.12189315572204</v>
+        <v>13.02619155534629</v>
       </c>
       <c r="O5" t="n">
-        <v>3.622415375922817</v>
+        <v>3.609181563089655</v>
       </c>
       <c r="P5" t="n">
-        <v>359.2798039009194</v>
+        <v>359.2863377491529</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33723,28 +33968,28 @@
         <v>0.0513</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1868637492622844</v>
+        <v>-0.1844322804094505</v>
       </c>
       <c r="J6" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="K6" t="n">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1646800021215512</v>
+        <v>0.1630512387269032</v>
       </c>
       <c r="M6" t="n">
-        <v>2.4472843548967</v>
+        <v>2.441415802257727</v>
       </c>
       <c r="N6" t="n">
-        <v>10.20163595917185</v>
+        <v>10.14698019108427</v>
       </c>
       <c r="O6" t="n">
-        <v>3.193999993608618</v>
+        <v>3.185432496708142</v>
       </c>
       <c r="P6" t="n">
-        <v>353.9492055383269</v>
+        <v>353.9234629588584</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33801,28 +34046,28 @@
         <v>0.0527</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.220556001749634</v>
+        <v>-0.2171037058010681</v>
       </c>
       <c r="J7" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="K7" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1558644894288784</v>
+        <v>0.1534956197934126</v>
       </c>
       <c r="M7" t="n">
-        <v>3.005563537530169</v>
+        <v>2.998584822707765</v>
       </c>
       <c r="N7" t="n">
-        <v>15.24882274874009</v>
+        <v>15.17997044912181</v>
       </c>
       <c r="O7" t="n">
-        <v>3.904974103466</v>
+        <v>3.896148155437856</v>
       </c>
       <c r="P7" t="n">
-        <v>348.8289918408269</v>
+        <v>348.7925700654219</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33879,28 +34124,28 @@
         <v>0.0469</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1926217909971983</v>
+        <v>-0.1886730534536729</v>
       </c>
       <c r="J8" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="K8" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1019578222100112</v>
+        <v>0.09941017952774933</v>
       </c>
       <c r="M8" t="n">
-        <v>3.304969701545801</v>
+        <v>3.299358356491027</v>
       </c>
       <c r="N8" t="n">
-        <v>18.91562013131968</v>
+        <v>18.8329850552812</v>
       </c>
       <c r="O8" t="n">
-        <v>4.34920913860436</v>
+        <v>4.339698728630963</v>
       </c>
       <c r="P8" t="n">
-        <v>348.8418621963251</v>
+        <v>348.8002037363262</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33957,28 +34202,28 @@
         <v>0.0369</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2851138805279991</v>
+        <v>-0.2809206513010929</v>
       </c>
       <c r="J9" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="K9" t="n">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1025913220434334</v>
+        <v>0.1012245594923461</v>
       </c>
       <c r="M9" t="n">
-        <v>4.980253085512732</v>
+        <v>4.961565884193516</v>
       </c>
       <c r="N9" t="n">
-        <v>40.95661455874743</v>
+        <v>40.7212223844045</v>
       </c>
       <c r="O9" t="n">
-        <v>6.399735506936785</v>
+        <v>6.38131823249746</v>
       </c>
       <c r="P9" t="n">
-        <v>343.0244992330556</v>
+        <v>342.9800988199942</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34035,28 +34280,28 @@
         <v>0.0206</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2452922345536498</v>
+        <v>-0.2530181148801365</v>
       </c>
       <c r="J10" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="K10" t="n">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06082502724169236</v>
+        <v>0.06522047202121051</v>
       </c>
       <c r="M10" t="n">
-        <v>5.961340094017492</v>
+        <v>5.956137367543562</v>
       </c>
       <c r="N10" t="n">
-        <v>53.51055905477838</v>
+        <v>53.32325576545056</v>
       </c>
       <c r="O10" t="n">
-        <v>7.315091185677618</v>
+        <v>7.302277436899433</v>
       </c>
       <c r="P10" t="n">
-        <v>341.1753862916643</v>
+        <v>341.2571575152495</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34094,7 +34339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K666"/>
+  <dimension ref="A1:K671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72031,6 +72276,291 @@
         </is>
       </c>
     </row>
+    <row r="667">
+      <c r="A667" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>-36.71145801605343,174.75083786476034</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>-36.71211748399934,174.75044241733931</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>-36.7128386392572,174.7502147165428</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>-36.7135912830862,174.75022580524526</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>-36.71431678851068,174.7502063999246</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>-36.71504232514436,174.75021024619403</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>-36.71576692621402,174.7502857750801</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>-36.71649820833967,174.7503640029838</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>-36.71722351737767,174.75046659140588</t>
+        </is>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>-36.71145750598507,174.7508363098519</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>-36.71211779115934,174.75044346967198</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>-36.71283878294165,174.75021547950314</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>-36.713591213181,174.75022457699802</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>-36.7143168773304,174.7502040518053</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>-36.715042749808276,174.750203887477</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>-36.715767555364216,174.75028011984583</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>-36.716501708713096,174.75034398437327</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>-36.71722482213381,174.7504598428314</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>-36.711457744016975,174.75083703547583</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>-36.71211855905928,174.7504461005036</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>-36.71283999399609,174.75022191016882</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>-36.71359148644676,174.75022937832819</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>-36.714316627789145,174.75021064890237</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>-36.715042064385656,174.75021415066936</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>-36.71576646977153,174.75028987789705</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>-36.71649878217161,174.75036072124448</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>-36.717224485422584,174.75046158439903</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>-36.71145672388023,174.750833925659</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>-36.7121183133313,174.75044525863748</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>-36.71284007610147,174.75022234614616</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>-36.7135915055118,174.75022971330472</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>-36.7143165643464,174.75021232613042</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>-36.71504184087808,174.75021749736248</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>-36.715765680249106,174.7502969746614</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>-36.71649683114267,174.75037187915785</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>-36.717223917222334,174.75046452329437</t>
+        </is>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>-36.71145614580269,174.7508321634295</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>-36.712118866219235,174.7504471528363</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>-36.71284128715552,174.75022877681204</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>-36.71359187410249,174.75023618951752</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>-36.71431649244458,174.7502142269889</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>-36.71504137896215,174.7502244138615</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>-36.71576521146994,174.75030118836514</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>-36.716495453945136,174.75037975533164</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>-36.71722094995321,174.7504798708582</t>
+        </is>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0155/nzd0155.xlsx
+++ b/data/nzd0155/nzd0155.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K671"/>
+  <dimension ref="A1:K675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26599,6 +26599,162 @@
         <v>330.43</v>
       </c>
       <c r="K671" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>334.72</v>
+      </c>
+      <c r="C672" t="n">
+        <v>331.81</v>
+      </c>
+      <c r="D672" t="n">
+        <v>338.44</v>
+      </c>
+      <c r="E672" t="n">
+        <v>352.89</v>
+      </c>
+      <c r="F672" t="n">
+        <v>351.28</v>
+      </c>
+      <c r="G672" t="n">
+        <v>346.18</v>
+      </c>
+      <c r="H672" t="n">
+        <v>346.94</v>
+      </c>
+      <c r="I672" t="n">
+        <v>338</v>
+      </c>
+      <c r="J672" t="n">
+        <v>330.1</v>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>334.96</v>
+      </c>
+      <c r="C673" t="n">
+        <v>332.37</v>
+      </c>
+      <c r="D673" t="n">
+        <v>338.75</v>
+      </c>
+      <c r="E673" t="n">
+        <v>353.02</v>
+      </c>
+      <c r="F673" t="n">
+        <v>351.26</v>
+      </c>
+      <c r="G673" t="n">
+        <v>346.12</v>
+      </c>
+      <c r="H673" t="n">
+        <v>346.79</v>
+      </c>
+      <c r="I673" t="n">
+        <v>337.66</v>
+      </c>
+      <c r="J673" t="n">
+        <v>331.18</v>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
+        <v>334.95</v>
+      </c>
+      <c r="C674" t="n">
+        <v>332.75</v>
+      </c>
+      <c r="D674" t="n">
+        <v>339.22</v>
+      </c>
+      <c r="E674" t="n">
+        <v>352.77</v>
+      </c>
+      <c r="F674" t="n">
+        <v>350.56</v>
+      </c>
+      <c r="G674" t="n">
+        <v>346.3</v>
+      </c>
+      <c r="H674" t="n">
+        <v>346.21</v>
+      </c>
+      <c r="I674" t="n">
+        <v>338.4</v>
+      </c>
+      <c r="J674" t="n">
+        <v>331.9</v>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>334.95</v>
+      </c>
+      <c r="C675" t="n">
+        <v>332.98</v>
+      </c>
+      <c r="D675" t="n">
+        <v>339.17</v>
+      </c>
+      <c r="E675" t="n">
+        <v>352.47</v>
+      </c>
+      <c r="F675" t="n">
+        <v>350.09</v>
+      </c>
+      <c r="G675" t="n">
+        <v>345.96</v>
+      </c>
+      <c r="H675" t="n">
+        <v>344.92</v>
+      </c>
+      <c r="I675" t="n">
+        <v>337.18</v>
+      </c>
+      <c r="J675" t="n">
+        <v>331.26</v>
+      </c>
+      <c r="K675" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26615,7 +26771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B687"/>
+  <dimension ref="A1:B691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33488,6 +33644,46 @@
       </c>
       <c r="B687" t="n">
         <v>-0.3</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>0.58</v>
       </c>
     </row>
   </sheetData>
@@ -33656,28 +33852,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4069803215152752</v>
+        <v>-0.4140497872275977</v>
       </c>
       <c r="J2" t="n">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="K2" t="n">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3739758763894523</v>
+        <v>0.3818682828087828</v>
       </c>
       <c r="M2" t="n">
-        <v>3.084875679646953</v>
+        <v>3.101586822715759</v>
       </c>
       <c r="N2" t="n">
-        <v>16.11322506933115</v>
+        <v>16.24112928445289</v>
       </c>
       <c r="O2" t="n">
-        <v>4.014128182972132</v>
+        <v>4.03002844710219</v>
       </c>
       <c r="P2" t="n">
-        <v>352.1074574003287</v>
+        <v>352.1825890751023</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33734,28 +33930,28 @@
         <v>0.0409</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4509613708819295</v>
+        <v>-0.4573201932569907</v>
       </c>
       <c r="J3" t="n">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="K3" t="n">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4239127384283863</v>
+        <v>0.4311702682461904</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08703410616915</v>
+        <v>3.103875563571422</v>
       </c>
       <c r="N3" t="n">
-        <v>16.06122481329985</v>
+        <v>16.14796838811958</v>
       </c>
       <c r="O3" t="n">
-        <v>4.007645794390998</v>
+        <v>4.018453482139564</v>
       </c>
       <c r="P3" t="n">
-        <v>350.2579578889014</v>
+        <v>350.3255317019149</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33812,28 +34008,28 @@
         <v>0.0409</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5033136640904552</v>
+        <v>-0.507060892557467</v>
       </c>
       <c r="J4" t="n">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="K4" t="n">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4185639345566653</v>
+        <v>0.4245900018946374</v>
       </c>
       <c r="M4" t="n">
-        <v>3.641299127636487</v>
+        <v>3.642633652247394</v>
       </c>
       <c r="N4" t="n">
-        <v>20.45058688497634</v>
+        <v>20.39254950545918</v>
       </c>
       <c r="O4" t="n">
-        <v>4.522232511158215</v>
+        <v>4.515811057325049</v>
       </c>
       <c r="P4" t="n">
-        <v>355.805998495508</v>
+        <v>355.845818643066</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33890,28 +34086,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2478547211844259</v>
+        <v>-0.2476137177796865</v>
       </c>
       <c r="J5" t="n">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="K5" t="n">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2151151701846582</v>
+        <v>0.2169805527142653</v>
       </c>
       <c r="M5" t="n">
-        <v>2.732309819719831</v>
+        <v>2.717502551938405</v>
       </c>
       <c r="N5" t="n">
-        <v>13.02619155534629</v>
+        <v>12.9492552278142</v>
       </c>
       <c r="O5" t="n">
-        <v>3.609181563089655</v>
+        <v>3.598507361089345</v>
       </c>
       <c r="P5" t="n">
-        <v>359.2863377491529</v>
+        <v>359.2837791563323</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33968,28 +34164,28 @@
         <v>0.0513</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1844322804094505</v>
+        <v>-0.1823015247729616</v>
       </c>
       <c r="J6" t="n">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="K6" t="n">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1630512387269032</v>
+        <v>0.1613656632346478</v>
       </c>
       <c r="M6" t="n">
-        <v>2.441415802257727</v>
+        <v>2.437785022042735</v>
       </c>
       <c r="N6" t="n">
-        <v>10.14698019108427</v>
+        <v>10.10847791741502</v>
       </c>
       <c r="O6" t="n">
-        <v>3.185432496708142</v>
+        <v>3.179383260542054</v>
       </c>
       <c r="P6" t="n">
-        <v>353.9234629588584</v>
+        <v>353.9008253156402</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34046,28 +34242,28 @@
         <v>0.0527</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2171037058010681</v>
+        <v>-0.2134373451012593</v>
       </c>
       <c r="J7" t="n">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="K7" t="n">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1534956197934126</v>
+        <v>0.1502616688663541</v>
       </c>
       <c r="M7" t="n">
-        <v>2.998584822707765</v>
+        <v>2.997074298931996</v>
       </c>
       <c r="N7" t="n">
-        <v>15.17997044912181</v>
+        <v>15.15053859419722</v>
       </c>
       <c r="O7" t="n">
-        <v>3.896148155437856</v>
+        <v>3.89236927772754</v>
       </c>
       <c r="P7" t="n">
-        <v>348.7925700654219</v>
+        <v>348.753744387839</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34124,28 +34320,28 @@
         <v>0.0469</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1886730534536729</v>
+        <v>-0.185805419729082</v>
       </c>
       <c r="J8" t="n">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="K8" t="n">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09941017952774933</v>
+        <v>0.09764806223833755</v>
       </c>
       <c r="M8" t="n">
-        <v>3.299358356491027</v>
+        <v>3.293474093484198</v>
       </c>
       <c r="N8" t="n">
-        <v>18.8329850552812</v>
+        <v>18.76200863715677</v>
       </c>
       <c r="O8" t="n">
-        <v>4.339698728630963</v>
+        <v>4.33151343495051</v>
       </c>
       <c r="P8" t="n">
-        <v>348.8002037363262</v>
+        <v>348.7698472125077</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34202,28 +34398,28 @@
         <v>0.0369</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2809206513010929</v>
+        <v>-0.2781398600234403</v>
       </c>
       <c r="J9" t="n">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="K9" t="n">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1012245594923461</v>
+        <v>0.1005186683980204</v>
       </c>
       <c r="M9" t="n">
-        <v>4.961565884193516</v>
+        <v>4.944288842210298</v>
       </c>
       <c r="N9" t="n">
-        <v>40.7212223844045</v>
+        <v>40.51497196036056</v>
       </c>
       <c r="O9" t="n">
-        <v>6.38131823249746</v>
+        <v>6.365137230285028</v>
       </c>
       <c r="P9" t="n">
-        <v>342.9800988199942</v>
+        <v>342.950547385845</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34280,28 +34476,28 @@
         <v>0.0206</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2530181148801365</v>
+        <v>-0.2567778407056289</v>
       </c>
       <c r="J10" t="n">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="K10" t="n">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06522047202121051</v>
+        <v>0.0677813000285018</v>
       </c>
       <c r="M10" t="n">
-        <v>5.956137367543562</v>
+        <v>5.940133608314972</v>
       </c>
       <c r="N10" t="n">
-        <v>53.32325576545056</v>
+        <v>53.07214648921548</v>
       </c>
       <c r="O10" t="n">
-        <v>7.302277436899433</v>
+        <v>7.285063245381984</v>
       </c>
       <c r="P10" t="n">
-        <v>341.2571575152495</v>
+        <v>341.2971089328746</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34339,7 +34535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K671"/>
+  <dimension ref="A1:K675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72561,6 +72757,234 @@
         </is>
       </c>
     </row>
+    <row r="672">
+      <c r="A672" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>-36.71145706392581,174.7508349622646</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>-36.71211987984703,174.7504506255342</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>-36.712841410313544,174.75022943077806</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>-36.713591924942556,174.7502370827883</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>-36.71431637824752,174.7502172459994</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>-36.71504140131292,174.7502240791922</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>-36.7157656925854,174.75029686377445</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>-36.7164986482775,174.75036148698365</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>-36.717221644420626,174.7504762788753</t>
+        </is>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>-36.71145788003519,174.75083745011807</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>-36.712121599942435,174.7504565185975</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>-36.71284204662993,174.7502328096026</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>-36.713592007557644,174.75023853435323</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>-36.714316386706564,174.750217022369</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>-36.71504144601448,174.7502234098536</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>-36.71576587762974,174.75029520047033</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>-36.71649929862027,174.75035776767908</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>-36.717219371617766,174.7504880344555</t>
+        </is>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>-36.71145784603064,174.7508373464575</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>-36.71212276714988,174.75046051746202</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>-36.71284301136748,174.75023793233666</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>-36.71359184868244,174.75023574288215</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>-36.71431668277284,174.7502091953047</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>-36.715041311909786,174.75022541786944</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>-36.715766593134376,174.75028876902763</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>-36.7164978831682,174.75036586263602</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>-36.71721785641522,174.7504958715085</t>
+        </is>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>-36.71145784603064,174.7508373464575</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>-36.71212347361746,174.75046293782748</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>-36.71284290873584,174.75023738736493</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>-36.71359165803213,174.7502323931169</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>-36.7143168815599,174.7502039399901</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>-36.715041565218606,174.75022162495063</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>-36.715768184514154,174.75027446461146</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>-36.71650021675106,174.75035251689602</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>-36.71721920326194,174.75048890523917</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
